--- a/TAM2.0_Sequencing_Prework_Enterprise_v0.1.xlsx
+++ b/TAM2.0_Sequencing_Prework_Enterprise_v0.1.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,27 +31,26 @@
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
     <font>
       <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="002F5496"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
@@ -59,8 +58,18 @@
       <sz val="9"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002F5496"/>
       <sz val="9"/>
     </font>
     <font>
@@ -72,13 +81,8 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="002F5496"/>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -87,12 +91,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -122,36 +136,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -519,51 +545,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="150" customWidth="1" min="1" max="1"/>
+    <col width="135" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TAM 2.0 sequencing pre-work — Enterprise  (geo × segment view; June workshop pack: Europe · APAC · Oceania)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="95" customHeight="1">
+          <t>TAM 2.0 sequencing pre-work — Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>READ ME FIRST — what this file is (per 12-Jun working session): 1) Unlike the Genius-UK PPT exercise, this is a GEO × SEGMENT view — the unit of sequencing is geo + segment (broken by persona only where it makes sense), NOT proposition. 2) Business priorities and corporate priorities/constraints are INPUTS to sequencing — captured up front with the timeline by which they must be met; propositions (Genius S, WP360, Revenue Boost, eCom…) appear there and as ▲ milestone annotations on the timeline, never as an axis. 3) Each geo tab captures the CURRENT-STATE stack and the TARGET-STATE stack before the timeline. 4) With those inputs, the Now / Next / Later columns sequence the three kinds of work per workstream: new feature build [BUILD], migration [MIGRATE] (+[STOP] constrain/stop-sell), and decom [EXIT].</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Terminology alignment (12-Jun): SALES MOTION = direct / partner-led / self-serve · PERSONA = partner/customer type within a segment (e.g. Referral, Agent, ISO/Wholesale, Payfac, PFaaS) · CHANNEL = digital / in-person / omnichannel · PROPOSITION = what the merchant buys (Genius S, WP360, Revenue Boost) — an input &amp; milestone, not an axis · PLATFORM = the stack (current vs target). Persona treatment: SMB = no persona split · Integrated = split by persona · Enterprise = TBD (region × vertical candidate — open decision).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="50" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Tags: [BUILD] target-state build / adherence · [MIGRATE] front-book switch, back-book migration, thin-out · [STOP] stop-sell / stop-integration / constrain (feeds Debt Book tranches) · [EXIT] decommission milestone. Motion tags [Direct]/[Bank]/[ISV] only where an implication is motion-specific. Horizons: Now = H2 '26 – H1 '27 · Next = H2 '27 – H1 '29 · Later = H2 '29+. Blue text = hypothesis — validate. Blank = input needed, not 'nothing planned'. (validate w/ SPOC) = no confirmed TAM linkage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Open questions for the group: 1) Which countries do we consider per region (avoid the long tail) — Europe list to confirm; APAC / Oceania scope to confirm. 2) Enterprise: do we split by persona / vertical (region × top 1–4 verticals) — decide before populating. 3) North America intentionally omitted from this June pack — sequenced for the Jul 20–21 in-person (US/Canada straw-man content preserved in SMB v0.3). 4) Non-UK&amp;I tabs carry pre-fill from the v0.2/v0.3 straw man for efficiency — validate or clear with each geo lead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise note: persona / vertical split TBD — candidate structure is region × top 1–4 priority verticals (airlines, gambling, QSR/FSR/Stadia…); decide before populating. Seeded items to validate: WP Total end-of-life — triPOS option currently points at MBoss (not the long-term answer); GMAS EU enterprise back-book → NAP migration as expansion unlock.</t>
+          <t>June workshop pack: Europe · APAC · Oceania</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Notes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1. Unlike the PPT exercise we did for Genius, this is a geo × segment view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2. It takes business priorities and corporate priorities as inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3. It captures the current-state and target-state stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4. It tracks BUILD, MIGRATE and DECOM decisions on a Now / Next / Later timeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>How to read each geo tab:</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>• The INPUTS box holds business priorities and corporate constraints, with the dates they must be met.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>• The Milestones row (▼) places proposition and corporate milestones over the horizon in which they land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>• The table has one row per workstream: current-state stack, target-state stack, then Now / Next / Later actions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>• Tags: [BUILD] = target-state build or adherence · [MIGRATE] = front-book switch, back-book migration or thin-out · [STOP] = stop-sell / stop-integration (frees capacity) · [EXIT] = decommission milestone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>• Horizons: Now = H2 '26 – H1 '27 · Next = H2 '27 – H1 '29 · Later = H2 '29+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>• Blue text is a hypothesis to validate. A blank cell means we need your input — not that nothing is planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Terminology:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>• Sales motion = direct, partner-led, or self-serve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>• Persona = the partner or customer type within a segment (e.g. Referral, Agent, ISO/Wholesale, Payfac, PFaaS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>• Channel = digital, in-person, or omnichannel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>• Proposition = what the merchant buys (e.g. Genius S, WP360, Revenue Boost). Propositions are inputs and milestones, not an axis of this view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>• Platform = the stack itself, current vs target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>• Persona treatment: SMB is not split by persona; Integrated is split by persona; Enterprise is to be decided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Open questions:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>1. Which countries do we consider per region? We want to avoid the long tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2. Enterprise: do we split by persona / vertical (region × top 1–4 verticals)? Decide before populating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>3. North America is intentionally omitted from this June pack — it is sequenced for the Jul 20–21 in-person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>4. Tabs other than UK&amp;I carry pre-fill from the earlier straw man — validate or clear with each geo lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise notes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>• Persona / vertical split is an open decision. The candidate structure is region × top 1–4 priority verticals (airlines, gambling, QSR/FSR/Stadia…). Decide before populating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>• Seeded item to validate: WP Total end-of-life — the triPOS option currently points at MBoss, which is not the long-term answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>• Seeded item to validate: GMAS EU enterprise back-book → NAP migration as the expansion unlock.</t>
         </is>
       </c>
     </row>
@@ -578,12 +772,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
@@ -592,212 +786,881 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>TAM 2.0 sequencing — Enterprise · Europe   (inputs first → current vs target stack → Now/Next/Later by workstream; see Notes tab)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="58" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Business priorities (segment lead; incl. timing to be met)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+          <t>TAM 2.0 sequencing — Enterprise · Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Business priorities</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Corporate priorities / constraints (hard dates, contractual, regulatory)</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Corporate priorities / constraints</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Proposition &amp; corporate milestones (▲ annotate on timeline — propositions are inputs, not axes)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>(populate ahead of June workshop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Workstream (boulder)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Current-state stack (today)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Target-state stack (decisions to date — validate)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>SEQUENCING — current stack → target stack → Now / Next / Later</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Current-state stack</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Target-state stack (validate)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Milestones ▼</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="12" t="inlineStr"/>
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Global API → API 2.0 / Global API ecosystem on Global Gateway · Payment Apps &amp; SDKs → PayApp 2.0 (Nucleus + triPOS hybrid; Yazara softPOS; Scalefusion + Sightstream TMS) · Developer experience → common portal + MCP server · Hosted solutions / plug-ins → target plug-in set on GP-API</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="110" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Global API
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• API 2.0 / Global API ecosystem on Global Gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Payment apps &amp; SDKs
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• PayApp 2.0 (Nucleus + triPOS hybrid)
+• Yazara softPOS
+• Scalefusion + Sightstream TMS</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Developer experience
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Common portal + MCP server</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Hosted solutions / plug-ins
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Target plug-in set on GP-API</t>
+          </r>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr"/>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Experience → Ignition (Horizon/Kirby + Launchpad converge) · Ingress → Boarding gateway · Orchestration → Workstream manager · Fulfillment → Actor &amp; PIL · Integration &amp; messaging → Kafka + Mulesoft · Ops data → hWP party model · CPQ → RCA · Credit &amp; underwriting → UCM</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
-    </row>
-    <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr"/>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Experience
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Ignition (Horizon/Kirby + Launchpad converge)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Ingress
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Boarding gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Orchestration
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Workstream manager</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fulfillment
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Actor &amp; PIL</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Integration &amp; messaging
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Kafka + Mulesoft</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Ops data
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP party model</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+CPQ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• RCA</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Credit &amp; underwriting
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• UCM</t>
+          </r>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr"/>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>CRM → 2/3 analysis in progress (OPEN TAM DECISION) · Servicing tools · Risk monitoring (merchant &amp; transaction)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9" ht="110" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">CRM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• 2/3 analysis in progress — OPEN TAM DECISION</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Servicing tools
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Risk monitoring
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Merchant &amp; transaction</t>
+          </r>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr"/>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Gateway → Global Gateway · Switch → PowerZac · Auth → RAFT (NA) + PowerZac (ROW) · Clearing → CORE (NA) + NAP (ROW) · APMs → GPPaaS (ROW)</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr"/>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Gateway
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Global Gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Switch
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• PowerZac</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Auth
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• RAFT (NA)
+• PowerZac (ROW)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Clearing
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• CORE (NA)
+• NAP (ROW)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+APMs
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• GPPaaS (ROW)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr"/>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Routing → Routing 2.0 · Gifts → Valutec · Network tokens → hWP tokens · Loyalty → Como · Fraud → Fraudsight · Managed optimization → Revenue Boost · FX / DCC / credential mgmt → hWP · 3DS / exemptions → hWP 3DS flex</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="110" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Routing
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Routing 2.0</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Gifts
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Valutec</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Network tokens
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP tokens</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Loyalty
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Como</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fraud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Fraudsight</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Managed optimization
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Revenue Boost</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+FX / DCC / credential mgmt
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+3DS / exemptions
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP 3DS flex</t>
+          </r>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr"/>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Data platforms → Snowflake + Iceberg · Master data → MDM</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Data platforms
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Snowflake + Iceberg</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Master data
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• MDM</t>
+          </r>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr"/>
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Global Infrastructure</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Design systems → WP DS foundation + Vega visual layer · Cloud · Observability</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="110" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr"/>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Design systems
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• WP DS foundation + Vega visual layer</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Cloud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Observability
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr"/>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Portal → MyAccount++ · Disputes → WDP · PFaaS → Converged PFaaS · Reporting → analysis in progress (OPEN)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr"/>
+      <c r="B17" s="14" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Portal
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• MyAccount++</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Disputes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• WDP</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+PFaaS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Converged PFaaS</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Reporting
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Analysis in progress — OPEN</t>
+          </r>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr"/>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:F2"/>
+  <mergeCells count="5">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -809,12 +1672,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
@@ -823,212 +1686,881 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>TAM 2.0 sequencing — Enterprise · APAC   (inputs first → current vs target stack → Now/Next/Later by workstream; see Notes tab)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="58" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Business priorities (segment lead; incl. timing to be met)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+          <t>TAM 2.0 sequencing — Enterprise · APAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Business priorities</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Corporate priorities / constraints (hard dates, contractual, regulatory)</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Corporate priorities / constraints</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Proposition &amp; corporate milestones (▲ annotate on timeline — propositions are inputs, not axes)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>(populate ahead of June workshop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Workstream (boulder)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Current-state stack (today)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Target-state stack (decisions to date — validate)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>SEQUENCING — current stack → target stack → Now / Next / Later</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Current-state stack</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Target-state stack (validate)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Milestones ▼</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="12" t="inlineStr"/>
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Global API → API 2.0 / Global API ecosystem on Global Gateway · Payment Apps &amp; SDKs → PayApp 2.0 (Nucleus + triPOS hybrid; Yazara softPOS; Scalefusion + Sightstream TMS) · Developer experience → common portal + MCP server · Hosted solutions / plug-ins → target plug-in set on GP-API</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="110" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Global API
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• API 2.0 / Global API ecosystem on Global Gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Payment apps &amp; SDKs
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• PayApp 2.0 (Nucleus + triPOS hybrid)
+• Yazara softPOS
+• Scalefusion + Sightstream TMS</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Developer experience
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Common portal + MCP server</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Hosted solutions / plug-ins
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Target plug-in set on GP-API</t>
+          </r>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr"/>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Experience → Ignition (Horizon/Kirby + Launchpad converge) · Ingress → Boarding gateway · Orchestration → Workstream manager · Fulfillment → Actor &amp; PIL · Integration &amp; messaging → Kafka + Mulesoft · Ops data → hWP party model · CPQ → RCA · Credit &amp; underwriting → UCM</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
-    </row>
-    <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr"/>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Experience
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Ignition (Horizon/Kirby + Launchpad converge)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Ingress
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Boarding gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Orchestration
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Workstream manager</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fulfillment
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Actor &amp; PIL</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Integration &amp; messaging
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Kafka + Mulesoft</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Ops data
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP party model</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+CPQ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• RCA</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Credit &amp; underwriting
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• UCM</t>
+          </r>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr"/>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>CRM → 2/3 analysis in progress (OPEN TAM DECISION) · Servicing tools · Risk monitoring (merchant &amp; transaction)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9" ht="110" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">CRM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• 2/3 analysis in progress — OPEN TAM DECISION</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Servicing tools
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Risk monitoring
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Merchant &amp; transaction</t>
+          </r>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr"/>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Gateway → Global Gateway · Switch → PowerZac · Auth → RAFT (NA) + PowerZac (ROW) · Clearing → CORE (NA) + NAP (ROW) · APMs → GPPaaS (ROW)</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr"/>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Gateway
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Global Gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Switch
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• PowerZac</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Auth
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• RAFT (NA)
+• PowerZac (ROW)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Clearing
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• CORE (NA)
+• NAP (ROW)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+APMs
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• GPPaaS (ROW)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr"/>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Routing → Routing 2.0 · Gifts → Valutec · Network tokens → hWP tokens · Loyalty → Como · Fraud → Fraudsight · Managed optimization → Revenue Boost · FX / DCC / credential mgmt → hWP · 3DS / exemptions → hWP 3DS flex</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="110" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Routing
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Routing 2.0</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Gifts
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Valutec</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Network tokens
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP tokens</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Loyalty
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Como</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fraud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Fraudsight</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Managed optimization
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Revenue Boost</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+FX / DCC / credential mgmt
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+3DS / exemptions
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP 3DS flex</t>
+          </r>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr"/>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Data platforms → Snowflake + Iceberg · Master data → MDM</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Data platforms
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Snowflake + Iceberg</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Master data
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• MDM</t>
+          </r>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr"/>
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Global Infrastructure</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Design systems → WP DS foundation + Vega visual layer · Cloud · Observability</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="110" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr"/>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Design systems
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• WP DS foundation + Vega visual layer</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Cloud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Observability
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr"/>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Portal → MyAccount++ · Disputes → WDP · PFaaS → Converged PFaaS · Reporting → analysis in progress (OPEN)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr"/>
+      <c r="B17" s="14" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Portal
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• MyAccount++</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Disputes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• WDP</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+PFaaS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Converged PFaaS</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Reporting
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Analysis in progress — OPEN</t>
+          </r>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr"/>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:F2"/>
+  <mergeCells count="5">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1040,12 +2572,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
@@ -1054,212 +2586,881 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>TAM 2.0 sequencing — Enterprise · Oceania   (inputs first → current vs target stack → Now/Next/Later by workstream; see Notes tab)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="58" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Business priorities (segment lead; incl. timing to be met)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+          <t>TAM 2.0 sequencing — Enterprise · Oceania</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Business priorities</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Corporate priorities / constraints (hard dates, contractual, regulatory)</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Corporate priorities / constraints</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>INPUT — Proposition &amp; corporate milestones (▲ annotate on timeline — propositions are inputs, not axes)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>(populate ahead of June workshop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Workstream (boulder)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Current-state stack (today)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Target-state stack (decisions to date — validate)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>SEQUENCING — current stack → target stack → Now / Next / Later</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Current-state stack</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Target-state stack (validate)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Milestones ▼</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="12" t="inlineStr"/>
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Global API → API 2.0 / Global API ecosystem on Global Gateway · Payment Apps &amp; SDKs → PayApp 2.0 (Nucleus + triPOS hybrid; Yazara softPOS; Scalefusion + Sightstream TMS) · Developer experience → common portal + MCP server · Hosted solutions / plug-ins → target plug-in set on GP-API</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="110" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Global API
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• API 2.0 / Global API ecosystem on Global Gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Payment apps &amp; SDKs
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• PayApp 2.0 (Nucleus + triPOS hybrid)
+• Yazara softPOS
+• Scalefusion + Sightstream TMS</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Developer experience
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Common portal + MCP server</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Hosted solutions / plug-ins
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Target plug-in set on GP-API</t>
+          </r>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr"/>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Experience → Ignition (Horizon/Kirby + Launchpad converge) · Ingress → Boarding gateway · Orchestration → Workstream manager · Fulfillment → Actor &amp; PIL · Integration &amp; messaging → Kafka + Mulesoft · Ops data → hWP party model · CPQ → RCA · Credit &amp; underwriting → UCM</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
-    </row>
-    <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr"/>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Experience
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Ignition (Horizon/Kirby + Launchpad converge)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Ingress
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Boarding gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Orchestration
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Workstream manager</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fulfillment
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Actor &amp; PIL</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Integration &amp; messaging
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Kafka + Mulesoft</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Ops data
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP party model</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+CPQ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• RCA</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Credit &amp; underwriting
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• UCM</t>
+          </r>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr"/>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>CRM → 2/3 analysis in progress (OPEN TAM DECISION) · Servicing tools · Risk monitoring (merchant &amp; transaction)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9" ht="110" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">CRM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• 2/3 analysis in progress — OPEN TAM DECISION</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Servicing tools
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Risk monitoring
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Merchant &amp; transaction</t>
+          </r>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr"/>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Gateway → Global Gateway · Switch → PowerZac · Auth → RAFT (NA) + PowerZac (ROW) · Clearing → CORE (NA) + NAP (ROW) · APMs → GPPaaS (ROW)</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr"/>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Gateway
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Global Gateway</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Switch
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• PowerZac</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Auth
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• RAFT (NA)
+• PowerZac (ROW)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Clearing
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• CORE (NA)
+• NAP (ROW)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+APMs
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• GPPaaS (ROW)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr"/>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Routing → Routing 2.0 · Gifts → Valutec · Network tokens → hWP tokens · Loyalty → Como · Fraud → Fraudsight · Managed optimization → Revenue Boost · FX / DCC / credential mgmt → hWP · 3DS / exemptions → hWP 3DS flex</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="110" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Routing
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Routing 2.0</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Gifts
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Valutec</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Network tokens
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP tokens</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Loyalty
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Como</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fraud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Fraudsight</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Managed optimization
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Revenue Boost</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+FX / DCC / credential mgmt
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+3DS / exemptions
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP 3DS flex</t>
+          </r>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr"/>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Data platforms → Snowflake + Iceberg · Master data → MDM</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Data platforms
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Snowflake + Iceberg</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Master data
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• MDM</t>
+          </r>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr"/>
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Global Infrastructure</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Design systems → WP DS foundation + Vega visual layer · Cloud · Observability</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="110" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr"/>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Design systems
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• WP DS foundation + Vega visual layer</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Cloud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Observability
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• (open)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr"/>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Portal → MyAccount++ · Disputes → WDP · PFaaS → Converged PFaaS · Reporting → analysis in progress (OPEN)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr"/>
+      <c r="B17" s="14" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">Portal
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• MyAccount++</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Disputes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• WDP</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+PFaaS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Converged PFaaS</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Reporting
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Analysis in progress — OPEN</t>
+          </r>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr"/>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:F2"/>
+  <mergeCells count="5">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TAM2.0_Sequencing_Prework_Enterprise_v0.1.xlsx
+++ b/TAM2.0_Sequencing_Prework_Enterprise_v0.1.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +60,10 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="002F5496"/>
       <sz val="9"/>
     </font>
     <font>
@@ -136,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -162,7 +166,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,13 +178,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -545,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="135" customWidth="1" min="1" max="1"/>
@@ -607,10 +614,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>• The INPUTS box holds business priorities and corporate constraints, with the dates they must be met.</t>
+          <t>• The INPUTS box holds business priorities, corporate constraints, and the data centre / infrastructure overlay, with the dates they must be met.</t>
         </is>
       </c>
     </row>
@@ -631,131 +638,152 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>• All timeline activities are TAM-scoped; BAU roadmap items are excluded. Where an activity directly enables a stated business priority, the cell says so: "[BUILD] … — enabling &lt;priority&gt;".</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>• Tags: [BUILD] = target-state build or adherence · [MIGRATE] = front-book switch, back-book migration or thin-out · [STOP] = stop-sell / stop-integration (frees capacity) · [EXIT] = decommission milestone.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>• Channel / persona context is tagged inline in square brackets where relevant, e.g. [Bank], [ISV], [Wholesale].</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>• Horizons: Now = H2 '26 – H1 '27 · Next = H2 '27 – H1 '29 · Later = H2 '29+.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>• Blue text is a hypothesis to validate. A blank cell means we need your input — not that nothing is planned.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Terminology:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>• Sales motion = direct, partner-led, or self-serve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>• Persona = the partner or customer type within a segment (e.g. Referral, Agent, ISO/Wholesale, Payfac, PFaaS).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>• Channel = digital, in-person, or omnichannel.</t>
+          <t>• Sales motion = direct, partner-led, or self-serve.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>• Proposition = what the merchant buys (e.g. Genius S, WP360, Revenue Boost). Propositions are inputs and milestones, not an axis of this view.</t>
+          <t>• Persona = the partner or customer type within a segment (e.g. Referral, Agent, ISO/Wholesale, Payfac, PFaaS).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>• Channel = digital, in-person, or omnichannel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>• Proposition = what the merchant buys (e.g. Genius S, WP360, Revenue Boost). Propositions are inputs and milestones, not an axis of this view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>• Platform = the stack itself, current vs target.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>• Persona treatment: SMB is not split by persona; Integrated is split by persona; Enterprise is to be decided.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>• Persona treatment: SMB is not split by persona; Integrated tags personas inline in brackets; Enterprise is to be decided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Open questions:</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>1. Which countries do we consider per region? We want to avoid the long tail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>2. Enterprise: do we split by persona / vertical (region × top 1–4 verticals)? Decide before populating.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3. North America is intentionally omitted from this June pack — it is sequenced for the Jul 20–21 in-person.</t>
+          <t>1. Which countries do we consider per region? We want to avoid the long tail.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>4. Tabs other than UK&amp;I carry pre-fill from the earlier straw man — validate or clear with each geo lead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise notes:</t>
+          <t>2. Enterprise: do we split by persona / vertical (region × top 1–4 verticals)? Decide before populating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>3. Reconcile platform retirement timelines with the data centre consolidation plan — preliminary view requested from infrastructure (an application kept for three years cannot sit in a data centre exiting in one).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>4. North America is intentionally omitted from this June pack — it is sequenced for the Jul 20–21 in-person.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>5. Tabs other than UK&amp;I carry pre-fill from the June QPRs and the earlier straw man — validate or clear with each geo lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise notes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>• Persona / vertical split is an open decision. The candidate structure is region × top 1–4 priority verticals (airlines, gambling, QSR/FSR/Stadia…). Decide before populating.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>• Seeded item to validate: WP Total end-of-life — the triPOS option currently points at MBoss, which is not the long-term answer.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>• Seeded item to validate: GMAS EU enterprise back-book → NAP migration as the expansion unlock.</t>
         </is>
@@ -772,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -821,65 +849,77 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Data centre &amp; infrastructure overlay</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Overlay required — application retirement dates must be reconciled with data centre decommissioning timelines (preliminary view requested from infrastructure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING — current stack → target stack → Now / Next / Later</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Current-state stack</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Target-state stack (validate)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Milestones ▼</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
-    </row>
-    <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -896,7 +936,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• API 2.0 / Global API ecosystem on Global Gateway</t>
+            <t>• API 2.0 / Global API on Global Gateway — federated build to the published spec (linting &amp; validation services)</t>
           </r>
           <r>
             <rPr>
@@ -956,18 +996,18 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
-    </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr"/>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1114,18 +1154,18 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1142,7 +1182,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• 2/3 analysis in progress — OPEN TAM DECISION</t>
+            <t>• iNASA at launch; target state under 2/3 analysis (decision pending)</t>
           </r>
           <r>
             <rPr>
@@ -1160,7 +1200,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
+            <t>• (to be defined)</t>
           </r>
           <r>
             <rPr>
@@ -1182,18 +1222,18 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
-    </row>
-    <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr"/>
+      <c r="F13" s="15" t="inlineStr"/>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1288,18 +1328,18 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1316,7 +1356,97 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• Routing 2.0</t>
+            <t>• Routing optimization service — RTR microservice + Prime capabilities extracted from RAFT</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Managed optimization
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Revenue Boost — single orchestration API across credentials, smart retry, fraud and 3DS microservices</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fraud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Fraudsight (powered by Ravelin)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+3DS / exemptions
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP 3DS Flex</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Network tokens / credentials
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP credential management</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Loyalty
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Como</t>
           </r>
           <r>
             <rPr>
@@ -1344,79 +1474,7 @@
               <u val="single"/>
             </rPr>
             <t xml:space="preserve">
-Network tokens
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• hWP tokens</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Loyalty
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Como</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Fraud
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Fraudsight</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Managed optimization
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Revenue Boost</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-FX / DCC / credential mgmt
+FX / DCC
 </t>
           </r>
           <r>
@@ -1426,38 +1484,20 @@
             </rPr>
             <t>• hWP</t>
           </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-3DS / exemptions
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• hWP 3DS flex</t>
-          </r>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1496,18 +1536,18 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Global Infrastructure</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1542,7 +1582,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
+            <t>• (to be defined)</t>
           </r>
           <r>
             <rPr>
@@ -1560,22 +1600,22 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
-          </r>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+            <t>• (to be defined)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr"/>
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1610,7 +1650,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• WDP</t>
+            <t>• WDP — north star (DMS interim for hGP; Merlin &amp; VAP disputes migrate to WDP in years 1–3; DMS converges to WDP in years 2–5)</t>
           </r>
           <r>
             <rPr>
@@ -1646,21 +1686,22 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• Analysis in progress — OPEN</t>
-          </r>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+            <t>• Target selection in progress (decision pending)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr"/>
+      <c r="F18" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1672,7 +1713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1721,65 +1762,77 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Data centre &amp; infrastructure overlay</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Overlay required — application retirement dates must be reconciled with data centre decommissioning timelines (preliminary view requested from infrastructure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING — current stack → target stack → Now / Next / Later</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Current-state stack</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Target-state stack (validate)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Milestones ▼</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
-    </row>
-    <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1796,7 +1849,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• API 2.0 / Global API ecosystem on Global Gateway</t>
+            <t>• API 2.0 / Global API on Global Gateway — federated build to the published spec (linting &amp; validation services)</t>
           </r>
           <r>
             <rPr>
@@ -1856,18 +1909,18 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
-    </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr"/>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2014,18 +2067,18 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2042,7 +2095,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• 2/3 analysis in progress — OPEN TAM DECISION</t>
+            <t>• iNASA at launch; target state under 2/3 analysis (decision pending)</t>
           </r>
           <r>
             <rPr>
@@ -2060,7 +2113,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
+            <t>• (to be defined)</t>
           </r>
           <r>
             <rPr>
@@ -2082,18 +2135,18 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
-    </row>
-    <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr"/>
+      <c r="F13" s="15" t="inlineStr"/>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2188,18 +2241,18 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2216,7 +2269,97 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• Routing 2.0</t>
+            <t>• Routing optimization service — RTR microservice + Prime capabilities extracted from RAFT</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Managed optimization
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Revenue Boost — single orchestration API across credentials, smart retry, fraud and 3DS microservices</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fraud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Fraudsight (powered by Ravelin)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+3DS / exemptions
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP 3DS Flex</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Network tokens / credentials
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP credential management</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Loyalty
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Como</t>
           </r>
           <r>
             <rPr>
@@ -2244,79 +2387,7 @@
               <u val="single"/>
             </rPr>
             <t xml:space="preserve">
-Network tokens
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• hWP tokens</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Loyalty
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Como</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Fraud
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Fraudsight</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Managed optimization
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Revenue Boost</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-FX / DCC / credential mgmt
+FX / DCC
 </t>
           </r>
           <r>
@@ -2326,38 +2397,20 @@
             </rPr>
             <t>• hWP</t>
           </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-3DS / exemptions
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• hWP 3DS flex</t>
-          </r>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2396,18 +2449,18 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Global Infrastructure</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2442,7 +2495,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
+            <t>• (to be defined)</t>
           </r>
           <r>
             <rPr>
@@ -2460,22 +2513,22 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
-          </r>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+            <t>• (to be defined)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr"/>
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2510,7 +2563,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• WDP</t>
+            <t>• WDP — north star (DMS interim for hGP; Merlin &amp; VAP disputes migrate to WDP in years 1–3; DMS converges to WDP in years 2–5)</t>
           </r>
           <r>
             <rPr>
@@ -2546,21 +2599,22 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• Analysis in progress — OPEN</t>
-          </r>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+            <t>• Target selection in progress (decision pending)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr"/>
+      <c r="F18" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2572,7 +2626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2621,65 +2675,77 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Data centre &amp; infrastructure overlay</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Overlay required — application retirement dates must be reconciled with data centre decommissioning timelines (preliminary view requested from infrastructure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING — current stack → target stack → Now / Next / Later</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Current-state stack</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Target-state stack (validate)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Milestones ▼</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
-    </row>
-    <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2696,7 +2762,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• API 2.0 / Global API ecosystem on Global Gateway</t>
+            <t>• API 2.0 / Global API on Global Gateway — federated build to the published spec (linting &amp; validation services)</t>
           </r>
           <r>
             <rPr>
@@ -2756,18 +2822,18 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
-    </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr"/>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2914,18 +2980,18 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2942,7 +3008,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• 2/3 analysis in progress — OPEN TAM DECISION</t>
+            <t>• iNASA at launch; target state under 2/3 analysis (decision pending)</t>
           </r>
           <r>
             <rPr>
@@ -2960,7 +3026,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
+            <t>• (to be defined)</t>
           </r>
           <r>
             <rPr>
@@ -2982,18 +3048,18 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
-    </row>
-    <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr"/>
+      <c r="F13" s="15" t="inlineStr"/>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3088,18 +3154,18 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3116,7 +3182,97 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• Routing 2.0</t>
+            <t>• Routing optimization service — RTR microservice + Prime capabilities extracted from RAFT</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Managed optimization
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Revenue Boost — single orchestration API across credentials, smart retry, fraud and 3DS microservices</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Fraud
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Fraudsight (powered by Ravelin)</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+3DS / exemptions
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP 3DS Flex</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Network tokens / credentials
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• hWP credential management</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+Loyalty
+</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="002F5496"/>
+              <sz val="9"/>
+            </rPr>
+            <t>• Como</t>
           </r>
           <r>
             <rPr>
@@ -3144,79 +3300,7 @@
               <u val="single"/>
             </rPr>
             <t xml:space="preserve">
-Network tokens
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• hWP tokens</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Loyalty
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Como</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Fraud
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Fraudsight</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-Managed optimization
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• Revenue Boost</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-FX / DCC / credential mgmt
+FX / DCC
 </t>
           </r>
           <r>
@@ -3226,38 +3310,20 @@
             </rPr>
             <t>• hWP</t>
           </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">
-3DS / exemptions
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="002F5496"/>
-              <sz val="9"/>
-            </rPr>
-            <t>• hWP 3DS flex</t>
-          </r>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3296,18 +3362,18 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Global Infrastructure</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3342,7 +3408,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
+            <t>• (to be defined)</t>
           </r>
           <r>
             <rPr>
@@ -3360,22 +3426,22 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• (open)</t>
-          </r>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+            <t>• (to be defined)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr"/>
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3410,7 +3476,7 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• WDP</t>
+            <t>• WDP — north star (DMS interim for hGP; Merlin &amp; VAP disputes migrate to WDP in years 1–3; DMS converges to WDP in years 2–5)</t>
           </r>
           <r>
             <rPr>
@@ -3446,21 +3512,22 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• Analysis in progress — OPEN</t>
-          </r>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+            <t>• Target selection in progress (decision pending)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr"/>
+      <c r="F18" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
